--- a/static/result.xlsx
+++ b/static/result.xlsx
@@ -468,28 +468,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Swapnil Pawar, Computer Engineer</t>
+          <t>Sandeep Chittakwar</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9404235881</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D2" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F2" t="n">
-        <v>115.5</v>
+        <v>136.5</v>
       </c>
       <c r="G2" t="n">
-        <v>66.67</v>
+        <v>82.76000000000001</v>
       </c>
     </row>
   </sheetData>
